--- a/artfynd/A 29661-2025 artfynd.xlsx
+++ b/artfynd/A 29661-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY138"/>
+  <dimension ref="A1:AZ138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74250124</t>
         </is>
       </c>
     </row>
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112293295</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14542263</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14576187</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14576195</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1365,6 +1395,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14576199</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14576200</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1589,6 +1629,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14576201</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1701,6 +1746,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14576202</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1841,6 +1891,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016966</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1971,6 +2026,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15677363</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2126,6 +2186,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16586768</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2281,6 +2346,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16586769</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2436,6 +2506,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16586770</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2593,6 +2668,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16586802</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2750,6 +2830,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16586807</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2907,6 +2992,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16586811</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3064,6 +3154,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16586812</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3221,6 +3316,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16586813</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3378,6 +3478,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16586821</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3506,6 +3611,11 @@
           <t>Väddnätfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61234073</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3634,6 +3744,11 @@
           <t>Väddnätfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61234086</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3762,6 +3877,11 @@
           <t>Väddnätfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61234087</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3890,6 +4010,11 @@
           <t>Väddnätfjäril inventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61234175</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4032,6 +4157,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520331</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4174,6 +4304,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520332</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4316,6 +4451,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520333</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4458,6 +4598,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520334</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4600,6 +4745,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520335</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4742,6 +4892,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520336</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4884,6 +5039,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520337</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5026,6 +5186,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520338</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5168,6 +5333,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520400</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5314,6 +5484,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520444</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5460,6 +5635,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520472</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5606,6 +5786,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520473</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5753,6 +5938,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520551</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5879,6 +6069,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65530030</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6005,6 +6200,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65530596</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6131,6 +6331,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65530598</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6257,6 +6462,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65530599</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6393,6 +6603,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67463521</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6529,6 +6744,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67463548</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6665,6 +6885,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67463550</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6801,6 +7026,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67463650</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6946,6 +7176,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916768</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7091,6 +7326,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916769</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7236,6 +7476,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916771</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7381,6 +7626,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916772</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7527,6 +7777,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916842</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7673,6 +7928,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916845</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7819,6 +8079,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916847</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7976,6 +8241,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73881434</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8133,6 +8403,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73881435</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8290,6 +8565,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73881436</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8447,6 +8727,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73881437</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8604,6 +8889,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73881464</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8761,6 +9051,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73881476</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8906,6 +9201,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181595</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9051,6 +9351,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181597</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9196,6 +9501,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181598</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9341,6 +9651,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181599</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9486,6 +9801,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181601</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9631,6 +9951,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181602</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9776,6 +10101,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181603</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9921,6 +10251,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181604</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -10066,6 +10401,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181615</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10211,6 +10551,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181616</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -10356,6 +10701,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181617</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10501,6 +10851,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181619</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10646,6 +11001,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181670</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10791,6 +11151,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181671</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10936,6 +11301,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181672</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11081,6 +11451,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181673</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11226,6 +11601,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181674</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11371,6 +11751,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181675</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11516,6 +11901,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181676</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11661,6 +12051,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181677</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11806,6 +12201,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181678</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11946,6 +12346,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143332</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -12087,6 +12492,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219837</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12228,6 +12638,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219843</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12369,6 +12784,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219844</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12510,6 +12930,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219845</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12645,6 +13070,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104177207</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12780,6 +13210,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104177208</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12915,6 +13350,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104177209</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -13050,6 +13490,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104177210</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -13190,6 +13635,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647245</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13330,6 +13780,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647246</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -13470,6 +13925,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647247</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -13610,6 +14070,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647248</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -13750,6 +14215,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647249</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -13890,6 +14360,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647250</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -14030,6 +14505,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647251</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -14170,6 +14650,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647302</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -14310,6 +14795,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647303</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -14450,6 +14940,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647306</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -14590,6 +15085,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647313</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -14730,6 +15230,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647314</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -14870,6 +15375,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647317</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -15010,6 +15520,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647323</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -15150,6 +15665,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618672</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -15290,6 +15810,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618673</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -15430,6 +15955,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618674</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -15570,6 +16100,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618675</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -15710,6 +16245,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618676</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -15850,6 +16390,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618677</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -15990,6 +16535,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618678</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -16130,6 +16680,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618679</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -16270,6 +16825,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618680</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -16410,6 +16970,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618736</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -16550,6 +17115,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618737</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -16690,6 +17260,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618738</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -16830,6 +17405,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618739</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -16970,6 +17550,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618741</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -17110,6 +17695,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016924</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -17250,6 +17840,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016925</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -17390,6 +17985,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016947</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -17530,6 +18130,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016948</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -17670,6 +18275,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016949</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -17810,6 +18420,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016950</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -17950,6 +18565,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016951</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -18090,6 +18710,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016952</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -18230,6 +18855,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016954</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -18370,6 +19000,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016955</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -18510,6 +19145,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016957</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -18650,6 +19290,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016964</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -18790,6 +19435,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016967</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -18930,6 +19580,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016968</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -19070,6 +19725,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016969</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -19210,6 +19870,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016970</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -19312,6 +19977,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14685537</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -19414,6 +20084,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14685536</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -19535,6 +20210,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65530043</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -19652,6 +20332,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65530644</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -19769,8 +20454,152 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65530646</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>